--- a/planejamento/cronograma2026.xlsx
+++ b/planejamento/cronograma2026.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
   <si>
     <t xml:space="preserve">LEGENDA             ======================================&gt; </t>
   </si>
@@ -231,6 +231,9 @@
   </si>
   <si>
     <t>Apresentação TCC</t>
+  </si>
+  <si>
+    <t>19/11/2026(pre feriado)</t>
   </si>
 </sst>
 </file>
@@ -534,6 +537,24 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="180" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -545,24 +566,6 @@
     </xf>
     <xf numFmtId="16" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="16" fontId="1" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="180" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -864,38 +867,38 @@
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="20"/>
       <c r="C1" s="6"/>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
-      <c r="L1" s="21"/>
-      <c r="M1" s="21"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="21"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="21"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
+      <c r="G1" s="27"/>
+      <c r="H1" s="27"/>
+      <c r="I1" s="27"/>
+      <c r="J1" s="27"/>
+      <c r="K1" s="27"/>
+      <c r="L1" s="27"/>
+      <c r="M1" s="27"/>
+      <c r="N1" s="27"/>
+      <c r="O1" s="27"/>
+      <c r="P1" s="27"/>
+      <c r="Q1" s="27"/>
       <c r="R1" s="3"/>
       <c r="S1" s="11"/>
-      <c r="T1" s="22" t="s">
+      <c r="T1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
-      <c r="W1" s="23"/>
-      <c r="X1" s="23"/>
-      <c r="Y1" s="23"/>
-      <c r="Z1" s="23"/>
-      <c r="AA1" s="23"/>
-      <c r="AB1" s="23"/>
-      <c r="AC1" s="23"/>
+      <c r="U1" s="29"/>
+      <c r="V1" s="29"/>
+      <c r="W1" s="29"/>
+      <c r="X1" s="29"/>
+      <c r="Y1" s="29"/>
+      <c r="Z1" s="29"/>
+      <c r="AA1" s="29"/>
+      <c r="AB1" s="29"/>
+      <c r="AC1" s="29"/>
     </row>
     <row r="2" spans="1:29" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
@@ -967,16 +970,16 @@
       <c r="W2" s="14">
         <v>46331</v>
       </c>
-      <c r="X2" s="27">
+      <c r="X2" s="23">
         <v>46338</v>
       </c>
-      <c r="Y2" s="27">
-        <v>46345</v>
-      </c>
-      <c r="Z2" s="29">
+      <c r="Y2" s="23" t="s">
+        <v>69</v>
+      </c>
+      <c r="Z2" s="25">
         <v>46352</v>
       </c>
-      <c r="AA2" s="29">
+      <c r="AA2" s="25">
         <v>46359</v>
       </c>
       <c r="AB2" s="14">
@@ -990,7 +993,7 @@
       <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="25"/>
+      <c r="B3" s="21"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -1023,7 +1026,7 @@
       <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="25"/>
+      <c r="B4" s="21"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
@@ -1056,7 +1059,7 @@
       <c r="A5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="25"/>
+      <c r="B5" s="21"/>
       <c r="C5" s="16" t="s">
         <v>40</v>
       </c>
@@ -1085,16 +1088,19 @@
         <v>67</v>
       </c>
       <c r="V5" s="15"/>
+      <c r="W5" s="16" t="s">
+        <v>58</v>
+      </c>
       <c r="X5" s="16" t="s">
         <v>58</v>
       </c>
       <c r="Y5" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="Z5" s="28" t="s">
+      <c r="Z5" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="AA5" s="28" t="s">
+      <c r="AA5" s="24" t="s">
         <v>68</v>
       </c>
       <c r="AB5" s="2"/>
@@ -1104,7 +1110,7 @@
       <c r="A6" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="25"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -1127,7 +1133,9 @@
       <c r="R6" s="3"/>
       <c r="T6" s="3"/>
       <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
+      <c r="W6" s="16" t="s">
+        <v>57</v>
+      </c>
       <c r="X6" s="16" t="s">
         <v>57</v>
       </c>
@@ -1141,7 +1149,7 @@
       <c r="A7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="25"/>
+      <c r="B7" s="21"/>
       <c r="C7" s="17"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
@@ -1174,7 +1182,7 @@
       <c r="A8" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="25"/>
+      <c r="B8" s="21"/>
       <c r="D8" s="16" t="s">
         <v>32</v>
       </c>
@@ -1217,7 +1225,7 @@
       <c r="A9" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="25"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
       <c r="F9" s="18" t="s">
@@ -1254,7 +1262,7 @@
       <c r="A10" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="25"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1327,7 +1335,7 @@
       <c r="A12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="25"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -1449,7 +1457,7 @@
       <c r="A15" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="25"/>
+      <c r="B15" s="21"/>
       <c r="C15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="18" t="s">
@@ -1528,7 +1536,7 @@
       <c r="A17" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="25"/>
+      <c r="B17" s="21"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1565,7 +1573,7 @@
       <c r="A18" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="25"/>
+      <c r="B18" s="21"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1599,7 +1607,7 @@
       <c r="A19" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="25"/>
+      <c r="B19" s="21"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1638,7 +1646,7 @@
       <c r="A20" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="25"/>
+      <c r="B20" s="21"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1671,7 +1679,7 @@
       <c r="A21" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="26"/>
+      <c r="B21" s="22"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>

--- a/planejamento/cronograma2026.xlsx
+++ b/planejamento/cronograma2026.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prof\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LAB4\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39E7CB3-F19D-4662-AB29-83392851E971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12330"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -19,12 +20,15 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="69">
   <si>
     <t xml:space="preserve">LEGENDA             ======================================&gt; </t>
   </si>
@@ -125,9 +129,6 @@
     <t>Elaboração das peguntas, explicação</t>
   </si>
   <si>
-    <t>Explicação Canvas</t>
-  </si>
-  <si>
     <t>Entrega em Apêncice e anexado ao sistema</t>
   </si>
   <si>
@@ -212,9 +213,6 @@
     <t xml:space="preserve">Critérios de </t>
   </si>
   <si>
-    <t>Inclusão da análise de concorrência que foi feito em março</t>
-  </si>
-  <si>
     <t>Entrega final Documentação</t>
   </si>
   <si>
@@ -234,12 +232,15 @@
   </si>
   <si>
     <t>19/11/2026(pre feriado)</t>
+  </si>
+  <si>
+    <t>Explicação Canvas Inclusão da análise de concorrência que foi feito em março</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -846,7 +847,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AC21"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="57" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -900,7 +901,7 @@
       <c r="AB1" s="29"/>
       <c r="AC1" s="29"/>
     </row>
-    <row r="2" spans="1:29" ht="93.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:29" ht="58.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
@@ -914,7 +915,7 @@
         <v>46170</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F2" s="1">
         <v>46184</v>
@@ -959,7 +960,7 @@
         <v>46303</v>
       </c>
       <c r="T2" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U2" s="14">
         <v>46317</v>
@@ -974,7 +975,7 @@
         <v>46338</v>
       </c>
       <c r="Y2" s="23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Z2" s="25">
         <v>46352</v>
@@ -1041,7 +1042,6 @@
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
       <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
@@ -1061,14 +1061,14 @@
       </c>
       <c r="B5" s="21"/>
       <c r="C5" s="16" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
       <c r="H5" s="16" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I5" s="15"/>
       <c r="J5" s="15"/>
@@ -1077,7 +1077,7 @@
       <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P5" s="15"/>
       <c r="Q5" s="15"/>
@@ -1085,23 +1085,23 @@
       <c r="S5" s="15"/>
       <c r="T5" s="15"/>
       <c r="U5" s="16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="V5" s="15"/>
       <c r="W5" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="X5" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Y5" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z5" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="Z5" s="24" t="s">
-        <v>68</v>
-      </c>
       <c r="AA5" s="24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="AB5" s="2"/>
       <c r="AC5" s="2"/>
@@ -1117,7 +1117,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -1126,7 +1126,7 @@
       <c r="M6" s="2"/>
       <c r="N6" s="2"/>
       <c r="O6" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
@@ -1134,10 +1134,10 @@
       <c r="T6" s="3"/>
       <c r="V6" s="3"/>
       <c r="W6" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="X6" s="16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" s="2"/>
@@ -1235,12 +1235,9 @@
         <v>26</v>
       </c>
       <c r="I9" s="3"/>
-      <c r="J9" s="16" t="s">
+      <c r="K9" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
       <c r="P9" s="3"/>
@@ -1312,7 +1309,7 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -1340,7 +1337,7 @@
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>29</v>
@@ -1350,15 +1347,15 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="18" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N12" s="16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="O12" s="3"/>
       <c r="P12" s="3"/>
       <c r="Q12" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
@@ -1377,19 +1374,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G13" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="G13" s="19" t="s">
-        <v>46</v>
-      </c>
       <c r="H13" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -1400,7 +1397,7 @@
       <c r="O13" s="3"/>
       <c r="P13" s="3"/>
       <c r="Q13" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
@@ -1420,7 +1417,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
@@ -1435,7 +1432,7 @@
       <c r="L14" s="3"/>
       <c r="M14" s="12"/>
       <c r="N14" s="16" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -1461,14 +1458,13 @@
       <c r="C15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="J15" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="K15" s="3"/>
+      <c r="K15" s="16" t="s">
+        <v>49</v>
+      </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
@@ -1476,10 +1472,10 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="S15" s="16" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="T15" s="3"/>
       <c r="V15" s="3"/>
@@ -1501,24 +1497,22 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="16" t="s">
-        <v>62</v>
-      </c>
+      <c r="J16" s="16"/>
       <c r="K16" s="18" t="s">
-        <v>33</v>
+        <v>68</v>
       </c>
       <c r="L16" s="18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M16" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="N16" s="19" t="s">
         <v>53</v>
-      </c>
-      <c r="N16" s="19" t="s">
-        <v>54</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
@@ -1553,10 +1547,10 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="S17" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T17" s="3"/>
       <c r="U17" s="3"/>
@@ -1593,7 +1587,7 @@
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
       <c r="U18" s="16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -1605,7 +1599,7 @@
     </row>
     <row r="19" spans="1:29" ht="57" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B19" s="21"/>
       <c r="C19" s="3"/>
@@ -1627,16 +1621,16 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="16" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="Z19" s="16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
